--- a/unit8_device_tree/unit8_device_tree.xlsx
+++ b/unit8_device_tree/unit8_device_tree.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\unit8_device_tree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBD92C9-FB42-418F-8CC3-004F10FCE6B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD3B225-04AA-4450-80F1-7AC160AD8C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{4DED5FC3-1A0F-4534-A4A0-3DE5C8B952C4}"/>
   </bookViews>
@@ -5128,6 +5128,8 @@
       <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5135,6 +5137,8 @@
       <sz val="16"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5142,6 +5146,8 @@
       <sz val="14"/>
       <color theme="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -5215,6 +5221,8 @@
       <sz val="14"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -5684,27 +5692,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
@@ -5802,6 +5789,27 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9872,118 +9880,118 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="15">
-      <c r="C4" s="91" t="s">
+      <c r="C4" s="140" t="s">
         <v>127</v>
       </c>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91" t="s">
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140" t="s">
         <v>128</v>
       </c>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="91"/>
-      <c r="J4" s="91" t="s">
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140" t="s">
         <v>129</v>
       </c>
-      <c r="K4" s="91"/>
-      <c r="L4" s="91"/>
-      <c r="M4" s="91"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
     </row>
     <row r="5" spans="1:13" ht="31.5" customHeight="1">
-      <c r="C5" s="90" t="s">
+      <c r="C5" s="139" t="s">
         <v>130</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="90"/>
-      <c r="F5" s="93" t="s">
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="142" t="s">
         <v>131</v>
       </c>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="92" t="s">
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="142"/>
+      <c r="J5" s="141" t="s">
         <v>132</v>
       </c>
-      <c r="K5" s="92"/>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
+      <c r="K5" s="141"/>
+      <c r="L5" s="141"/>
+      <c r="M5" s="141"/>
     </row>
     <row r="6" spans="1:13" ht="30" customHeight="1">
-      <c r="C6" s="90" t="s">
+      <c r="C6" s="139" t="s">
         <v>133</v>
       </c>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="93" t="s">
+      <c r="D6" s="139"/>
+      <c r="E6" s="139"/>
+      <c r="F6" s="142" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="93"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="93"/>
-      <c r="J6" s="92" t="s">
+      <c r="G6" s="142"/>
+      <c r="H6" s="142"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="141" t="s">
         <v>135</v>
       </c>
-      <c r="K6" s="92"/>
-      <c r="L6" s="92"/>
-      <c r="M6" s="92"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="141"/>
+      <c r="M6" s="141"/>
     </row>
     <row r="7" spans="1:13" ht="32.25" customHeight="1">
-      <c r="C7" s="90" t="s">
+      <c r="C7" s="139" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="90"/>
-      <c r="F7" s="93" t="s">
+      <c r="D7" s="139"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="142" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="93"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="93"/>
-      <c r="J7" s="92" t="s">
+      <c r="G7" s="142"/>
+      <c r="H7" s="142"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="141" t="s">
         <v>138</v>
       </c>
-      <c r="K7" s="92"/>
-      <c r="L7" s="92"/>
-      <c r="M7" s="92"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
     </row>
     <row r="8" spans="1:13" ht="18" customHeight="1">
-      <c r="C8" s="90" t="s">
+      <c r="C8" s="139" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="90"/>
-      <c r="E8" s="90"/>
-      <c r="F8" s="93" t="s">
+      <c r="D8" s="139"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="142" t="s">
         <v>140</v>
       </c>
-      <c r="G8" s="93"/>
-      <c r="H8" s="93"/>
-      <c r="I8" s="93"/>
-      <c r="J8" s="92" t="s">
+      <c r="G8" s="142"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="142"/>
+      <c r="J8" s="141" t="s">
         <v>141</v>
       </c>
-      <c r="K8" s="92"/>
-      <c r="L8" s="92"/>
-      <c r="M8" s="92"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="141"/>
+      <c r="M8" s="141"/>
     </row>
     <row r="9" spans="1:13" ht="24" customHeight="1">
-      <c r="C9" s="90" t="s">
+      <c r="C9" s="139" t="s">
         <v>142</v>
       </c>
-      <c r="D9" s="90"/>
-      <c r="E9" s="90"/>
-      <c r="F9" s="93" t="s">
+      <c r="D9" s="139"/>
+      <c r="E9" s="139"/>
+      <c r="F9" s="142" t="s">
         <v>143</v>
       </c>
-      <c r="G9" s="93"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="93"/>
-      <c r="J9" s="92" t="s">
+      <c r="G9" s="142"/>
+      <c r="H9" s="142"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="141" t="s">
         <v>144</v>
       </c>
-      <c r="K9" s="92"/>
-      <c r="L9" s="92"/>
-      <c r="M9" s="92"/>
+      <c r="K9" s="141"/>
+      <c r="L9" s="141"/>
+      <c r="M9" s="141"/>
     </row>
     <row r="12" spans="1:13" s="72" customFormat="1" ht="23.25">
       <c r="A12" s="70"/>
@@ -12011,35 +12019,37 @@
       <c r="B12" s="78" t="s">
         <v>323</v>
       </c>
-      <c r="AB12" s="83" t="s">
+      <c r="AA12" s="143" t="s">
         <v>621</v>
       </c>
-      <c r="AC12" s="84"/>
-      <c r="AL12" s="94" t="s">
+      <c r="AB12" s="144"/>
+      <c r="AC12" s="144"/>
+      <c r="AD12" s="145"/>
+      <c r="AL12" s="143" t="s">
         <v>622</v>
       </c>
-      <c r="AM12" s="95"/>
-      <c r="AN12" s="95"/>
-      <c r="AO12" s="95"/>
-      <c r="AP12" s="95"/>
-      <c r="AQ12" s="95"/>
-      <c r="AR12" s="96"/>
-      <c r="BC12" s="94" t="s">
+      <c r="AM12" s="144"/>
+      <c r="AN12" s="144"/>
+      <c r="AO12" s="144"/>
+      <c r="AP12" s="144"/>
+      <c r="AQ12" s="144"/>
+      <c r="AR12" s="145"/>
+      <c r="BC12" s="143" t="s">
         <v>633</v>
       </c>
-      <c r="BD12" s="95"/>
-      <c r="BE12" s="95"/>
-      <c r="BF12" s="96"/>
-      <c r="BM12" s="94" t="s">
+      <c r="BD12" s="144"/>
+      <c r="BE12" s="144"/>
+      <c r="BF12" s="145"/>
+      <c r="BM12" s="143" t="s">
         <v>636</v>
       </c>
-      <c r="BN12" s="95"/>
-      <c r="BO12" s="95"/>
-      <c r="BP12" s="95"/>
-      <c r="BQ12" s="95"/>
-      <c r="BR12" s="95"/>
-      <c r="BS12" s="95"/>
-      <c r="BT12" s="96"/>
+      <c r="BN12" s="144"/>
+      <c r="BO12" s="144"/>
+      <c r="BP12" s="144"/>
+      <c r="BQ12" s="144"/>
+      <c r="BR12" s="144"/>
+      <c r="BS12" s="144"/>
+      <c r="BT12" s="145"/>
     </row>
     <row r="13" spans="1:72">
       <c r="C13" s="67" t="s">
@@ -14335,10 +14345,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="BC12:BF12"/>
     <mergeCell ref="AL12:AR12"/>
     <mergeCell ref="BM12:BT12"/>
+    <mergeCell ref="AA12:AD12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" location="'gpio BBB'!A1" display="1.1 Device Tree Source (.dts)" xr:uid="{AF2CD107-6249-4937-9A23-4E39D12D5B20}"/>
@@ -14355,53 +14366,53 @@
   <sheetData>
     <row r="1" spans="2:37" ht="15" thickBot="1"/>
     <row r="2" spans="2:37" ht="23.25">
-      <c r="B2" s="97" t="s">
+      <c r="B2" s="90" t="s">
         <v>639</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="99"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
+      <c r="E2" s="91"/>
+      <c r="F2" s="91"/>
+      <c r="G2" s="91"/>
+      <c r="H2" s="91"/>
+      <c r="I2" s="91"/>
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="91"/>
+      <c r="S2" s="91"/>
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="91"/>
+      <c r="X2" s="91"/>
+      <c r="Y2" s="92"/>
       <c r="AI2" s="64" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="3" spans="2:37" ht="20.25">
-      <c r="B3" s="100"/>
-      <c r="C3" s="101" t="s">
+      <c r="B3" s="93"/>
+      <c r="C3" s="94" t="s">
         <v>641</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="102"/>
-      <c r="M3" s="102"/>
-      <c r="N3" s="102"/>
-      <c r="O3" s="102"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
       <c r="P3" s="15"/>
       <c r="Q3" s="15"/>
       <c r="R3" s="15"/>
@@ -14411,15 +14422,15 @@
       <c r="V3" s="15"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
-      <c r="Y3" s="103"/>
+      <c r="Y3" s="96"/>
       <c r="AJ3" s="78" t="s">
         <v>642</v>
       </c>
     </row>
     <row r="4" spans="2:37" ht="17.25">
-      <c r="B4" s="100"/>
+      <c r="B4" s="93"/>
       <c r="C4" s="15"/>
-      <c r="D4" s="104" t="s">
+      <c r="D4" s="97" t="s">
         <v>643</v>
       </c>
       <c r="E4" s="15"/>
@@ -14442,15 +14453,15 @@
       <c r="V4" s="15"/>
       <c r="W4" s="15"/>
       <c r="X4" s="15"/>
-      <c r="Y4" s="103"/>
+      <c r="Y4" s="96"/>
       <c r="AK4" t="s">
         <v>644</v>
       </c>
     </row>
     <row r="5" spans="2:37" ht="17.25">
-      <c r="B5" s="100"/>
+      <c r="B5" s="93"/>
       <c r="C5" s="15"/>
-      <c r="D5" s="104" t="s">
+      <c r="D5" s="97" t="s">
         <v>645</v>
       </c>
       <c r="E5" s="15"/>
@@ -14473,29 +14484,29 @@
       <c r="V5" s="15"/>
       <c r="W5" s="15"/>
       <c r="X5" s="15"/>
-      <c r="Y5" s="103"/>
+      <c r="Y5" s="96"/>
       <c r="AK5" t="s">
         <v>646</v>
       </c>
     </row>
     <row r="6" spans="2:37" ht="18">
-      <c r="B6" s="100"/>
-      <c r="C6" s="105" t="s">
+      <c r="B6" s="93"/>
+      <c r="C6" s="98" t="s">
         <v>647</v>
       </c>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="106"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="99"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="99"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="99"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="99"/>
+      <c r="N6" s="99"/>
+      <c r="O6" s="99"/>
+      <c r="P6" s="99"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="15"/>
       <c r="S6" s="15"/>
@@ -14504,15 +14515,15 @@
       <c r="V6" s="15"/>
       <c r="W6" s="15"/>
       <c r="X6" s="15"/>
-      <c r="Y6" s="103"/>
+      <c r="Y6" s="96"/>
       <c r="AK6" t="s">
         <v>648</v>
       </c>
     </row>
     <row r="7" spans="2:37" ht="17.25">
-      <c r="B7" s="100"/>
+      <c r="B7" s="93"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="97" t="s">
         <v>649</v>
       </c>
       <c r="E7" s="15"/>
@@ -14535,12 +14546,12 @@
       <c r="V7" s="15"/>
       <c r="W7" s="15"/>
       <c r="X7" s="15"/>
-      <c r="Y7" s="103"/>
+      <c r="Y7" s="96"/>
     </row>
     <row r="8" spans="2:37" ht="17.25">
-      <c r="B8" s="100"/>
+      <c r="B8" s="93"/>
       <c r="C8" s="15"/>
-      <c r="D8" s="104" t="s">
+      <c r="D8" s="97" t="s">
         <v>650</v>
       </c>
       <c r="E8" s="15"/>
@@ -14563,12 +14574,12 @@
       <c r="V8" s="15"/>
       <c r="W8" s="15"/>
       <c r="X8" s="15"/>
-      <c r="Y8" s="103"/>
+      <c r="Y8" s="96"/>
     </row>
     <row r="9" spans="2:37" ht="17.25">
-      <c r="B9" s="100"/>
+      <c r="B9" s="93"/>
       <c r="C9" s="15"/>
-      <c r="D9" s="104" t="s">
+      <c r="D9" s="97" t="s">
         <v>651</v>
       </c>
       <c r="E9" s="15"/>
@@ -14591,40 +14602,40 @@
       <c r="V9" s="15"/>
       <c r="W9" s="15"/>
       <c r="X9" s="15"/>
-      <c r="Y9" s="103"/>
+      <c r="Y9" s="96"/>
     </row>
     <row r="10" spans="2:37" ht="18">
-      <c r="B10" s="100"/>
-      <c r="C10" s="105" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="98" t="s">
         <v>652</v>
       </c>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="106"/>
-      <c r="G10" s="106"/>
-      <c r="H10" s="106"/>
-      <c r="I10" s="106"/>
-      <c r="J10" s="106"/>
-      <c r="K10" s="106"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="106"/>
-      <c r="N10" s="106"/>
-      <c r="O10" s="106"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="106"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="99"/>
+      <c r="F10" s="99"/>
+      <c r="G10" s="99"/>
+      <c r="H10" s="99"/>
+      <c r="I10" s="99"/>
+      <c r="J10" s="99"/>
+      <c r="K10" s="99"/>
+      <c r="L10" s="99"/>
+      <c r="M10" s="99"/>
+      <c r="N10" s="99"/>
+      <c r="O10" s="99"/>
+      <c r="P10" s="99"/>
+      <c r="Q10" s="99"/>
+      <c r="R10" s="99"/>
+      <c r="S10" s="99"/>
       <c r="T10" s="15"/>
       <c r="U10" s="15"/>
       <c r="V10" s="15"/>
       <c r="W10" s="15"/>
       <c r="X10" s="15"/>
-      <c r="Y10" s="103"/>
+      <c r="Y10" s="96"/>
     </row>
     <row r="11" spans="2:37" ht="17.25">
-      <c r="B11" s="100"/>
+      <c r="B11" s="93"/>
       <c r="C11" s="15"/>
-      <c r="D11" s="104" t="s">
+      <c r="D11" s="97" t="s">
         <v>653</v>
       </c>
       <c r="E11" s="15"/>
@@ -14647,12 +14658,12 @@
       <c r="V11" s="15"/>
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
-      <c r="Y11" s="103"/>
+      <c r="Y11" s="96"/>
     </row>
     <row r="12" spans="2:37" ht="17.25">
-      <c r="B12" s="100"/>
+      <c r="B12" s="93"/>
       <c r="C12" s="15"/>
-      <c r="D12" s="104" t="s">
+      <c r="D12" s="97" t="s">
         <v>654</v>
       </c>
       <c r="E12" s="15"/>
@@ -14675,40 +14686,40 @@
       <c r="V12" s="15"/>
       <c r="W12" s="15"/>
       <c r="X12" s="15"/>
-      <c r="Y12" s="103"/>
+      <c r="Y12" s="96"/>
     </row>
     <row r="13" spans="2:37" ht="18">
-      <c r="B13" s="100"/>
-      <c r="C13" s="105" t="s">
+      <c r="B13" s="93"/>
+      <c r="C13" s="98" t="s">
         <v>655</v>
       </c>
-      <c r="D13" s="106"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="106"/>
-      <c r="G13" s="106"/>
-      <c r="H13" s="106"/>
-      <c r="I13" s="106"/>
-      <c r="J13" s="106"/>
-      <c r="K13" s="106"/>
-      <c r="L13" s="106"/>
-      <c r="M13" s="106"/>
-      <c r="N13" s="106"/>
-      <c r="O13" s="106"/>
-      <c r="P13" s="106"/>
-      <c r="Q13" s="106"/>
-      <c r="R13" s="106"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="99"/>
+      <c r="L13" s="99"/>
+      <c r="M13" s="99"/>
+      <c r="N13" s="99"/>
+      <c r="O13" s="99"/>
+      <c r="P13" s="99"/>
+      <c r="Q13" s="99"/>
+      <c r="R13" s="99"/>
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
       <c r="U13" s="15"/>
       <c r="V13" s="15"/>
       <c r="W13" s="15"/>
       <c r="X13" s="15"/>
-      <c r="Y13" s="103"/>
+      <c r="Y13" s="96"/>
     </row>
     <row r="14" spans="2:37" ht="17.25">
-      <c r="B14" s="100"/>
+      <c r="B14" s="93"/>
       <c r="C14" s="15"/>
-      <c r="D14" s="104" t="s">
+      <c r="D14" s="97" t="s">
         <v>656</v>
       </c>
       <c r="E14" s="15"/>
@@ -14731,19 +14742,19 @@
       <c r="V14" s="15"/>
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
-      <c r="Y14" s="103"/>
+      <c r="Y14" s="96"/>
     </row>
     <row r="15" spans="2:37" ht="18">
-      <c r="B15" s="100"/>
-      <c r="C15" s="105" t="s">
+      <c r="B15" s="93"/>
+      <c r="C15" s="98" t="s">
         <v>657</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="106"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="106"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="106"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="99"/>
       <c r="J15" s="15"/>
       <c r="K15" s="15"/>
       <c r="L15" s="15"/>
@@ -14759,12 +14770,12 @@
       <c r="V15" s="15"/>
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
-      <c r="Y15" s="103"/>
+      <c r="Y15" s="96"/>
     </row>
     <row r="16" spans="2:37" ht="17.25">
-      <c r="B16" s="100"/>
+      <c r="B16" s="93"/>
       <c r="C16" s="15"/>
-      <c r="D16" s="104" t="s">
+      <c r="D16" s="97" t="s">
         <v>658</v>
       </c>
       <c r="E16" s="15"/>
@@ -14787,23 +14798,23 @@
       <c r="V16" s="15"/>
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
-      <c r="Y16" s="103"/>
+      <c r="Y16" s="96"/>
     </row>
     <row r="17" spans="1:25" ht="18">
-      <c r="B17" s="100"/>
-      <c r="C17" s="105" t="s">
+      <c r="B17" s="93"/>
+      <c r="C17" s="98" t="s">
         <v>659</v>
       </c>
-      <c r="D17" s="106"/>
-      <c r="E17" s="106"/>
-      <c r="F17" s="106"/>
-      <c r="G17" s="106"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="99"/>
+      <c r="J17" s="99"/>
+      <c r="K17" s="99"/>
+      <c r="L17" s="99"/>
+      <c r="M17" s="99"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
@@ -14815,12 +14826,12 @@
       <c r="V17" s="15"/>
       <c r="W17" s="15"/>
       <c r="X17" s="15"/>
-      <c r="Y17" s="103"/>
+      <c r="Y17" s="96"/>
     </row>
     <row r="18" spans="1:25" ht="17.25">
-      <c r="B18" s="100"/>
+      <c r="B18" s="93"/>
       <c r="C18" s="15"/>
-      <c r="D18" s="104" t="s">
+      <c r="D18" s="97" t="s">
         <v>660</v>
       </c>
       <c r="E18" s="15"/>
@@ -14843,40 +14854,40 @@
       <c r="V18" s="15"/>
       <c r="W18" s="15"/>
       <c r="X18" s="15"/>
-      <c r="Y18" s="103"/>
+      <c r="Y18" s="96"/>
     </row>
     <row r="19" spans="1:25" ht="18">
-      <c r="B19" s="100"/>
-      <c r="C19" s="105" t="s">
+      <c r="B19" s="93"/>
+      <c r="C19" s="98" t="s">
         <v>661</v>
       </c>
-      <c r="D19" s="106"/>
-      <c r="E19" s="106"/>
-      <c r="F19" s="106"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="106"/>
-      <c r="I19" s="106"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="106"/>
-      <c r="L19" s="106"/>
-      <c r="M19" s="106"/>
-      <c r="N19" s="106"/>
-      <c r="O19" s="106"/>
-      <c r="P19" s="106"/>
-      <c r="Q19" s="106"/>
-      <c r="R19" s="106"/>
+      <c r="D19" s="99"/>
+      <c r="E19" s="99"/>
+      <c r="F19" s="99"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="99"/>
+      <c r="I19" s="99"/>
+      <c r="J19" s="99"/>
+      <c r="K19" s="99"/>
+      <c r="L19" s="99"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="99"/>
+      <c r="O19" s="99"/>
+      <c r="P19" s="99"/>
+      <c r="Q19" s="99"/>
+      <c r="R19" s="99"/>
       <c r="S19" s="15"/>
       <c r="T19" s="15"/>
       <c r="U19" s="15"/>
       <c r="V19" s="15"/>
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
-      <c r="Y19" s="103"/>
+      <c r="Y19" s="96"/>
     </row>
     <row r="20" spans="1:25" ht="17.25">
-      <c r="B20" s="100"/>
+      <c r="B20" s="93"/>
       <c r="C20" s="15"/>
-      <c r="D20" s="104" t="s">
+      <c r="D20" s="97" t="s">
         <v>662</v>
       </c>
       <c r="E20" s="15"/>
@@ -14899,26 +14910,26 @@
       <c r="V20" s="15"/>
       <c r="W20" s="15"/>
       <c r="X20" s="15"/>
-      <c r="Y20" s="103"/>
+      <c r="Y20" s="96"/>
     </row>
     <row r="21" spans="1:25" ht="18">
-      <c r="B21" s="100"/>
-      <c r="C21" s="105" t="s">
+      <c r="B21" s="93"/>
+      <c r="C21" s="98" t="s">
         <v>663</v>
       </c>
-      <c r="D21" s="106"/>
-      <c r="E21" s="106"/>
-      <c r="F21" s="106"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="106"/>
-      <c r="I21" s="106"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="106"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="106"/>
-      <c r="N21" s="106"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="106"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="99"/>
+      <c r="M21" s="99"/>
+      <c r="N21" s="99"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="99"/>
       <c r="Q21" s="15"/>
       <c r="R21" s="15"/>
       <c r="S21" s="15"/>
@@ -14927,12 +14938,12 @@
       <c r="V21" s="15"/>
       <c r="W21" s="15"/>
       <c r="X21" s="15"/>
-      <c r="Y21" s="103"/>
+      <c r="Y21" s="96"/>
     </row>
     <row r="22" spans="1:25" ht="17.25">
-      <c r="B22" s="100"/>
+      <c r="B22" s="93"/>
       <c r="C22" s="15"/>
-      <c r="D22" s="104" t="s">
+      <c r="D22" s="97" t="s">
         <v>664</v>
       </c>
       <c r="E22" s="15"/>
@@ -14955,27 +14966,27 @@
       <c r="V22" s="15"/>
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
-      <c r="Y22" s="103"/>
+      <c r="Y22" s="96"/>
     </row>
     <row r="23" spans="1:25" ht="18">
-      <c r="B23" s="100"/>
-      <c r="C23" s="105" t="s">
+      <c r="B23" s="93"/>
+      <c r="C23" s="98" t="s">
         <v>665</v>
       </c>
-      <c r="D23" s="106"/>
-      <c r="E23" s="106"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="106"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="106"/>
-      <c r="L23" s="106"/>
-      <c r="M23" s="106"/>
-      <c r="N23" s="106"/>
-      <c r="O23" s="106"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="106"/>
+      <c r="D23" s="99"/>
+      <c r="E23" s="99"/>
+      <c r="F23" s="99"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="99"/>
+      <c r="I23" s="99"/>
+      <c r="J23" s="99"/>
+      <c r="K23" s="99"/>
+      <c r="L23" s="99"/>
+      <c r="M23" s="99"/>
+      <c r="N23" s="99"/>
+      <c r="O23" s="99"/>
+      <c r="P23" s="99"/>
+      <c r="Q23" s="99"/>
       <c r="R23" s="15"/>
       <c r="S23" s="15"/>
       <c r="T23" s="15"/>
@@ -14983,12 +14994,12 @@
       <c r="V23" s="15"/>
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
-      <c r="Y23" s="103"/>
+      <c r="Y23" s="96"/>
     </row>
     <row r="24" spans="1:25" ht="16.5" customHeight="1">
-      <c r="B24" s="100"/>
+      <c r="B24" s="93"/>
       <c r="C24" s="15"/>
-      <c r="D24" s="104" t="s">
+      <c r="D24" s="97" t="s">
         <v>666</v>
       </c>
       <c r="E24" s="15"/>
@@ -15011,40 +15022,40 @@
       <c r="V24" s="15"/>
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
-      <c r="Y24" s="103"/>
+      <c r="Y24" s="96"/>
     </row>
     <row r="25" spans="1:25" ht="18">
-      <c r="B25" s="100"/>
-      <c r="C25" s="105" t="s">
+      <c r="B25" s="93"/>
+      <c r="C25" s="98" t="s">
         <v>667</v>
       </c>
-      <c r="D25" s="106"/>
-      <c r="E25" s="106"/>
-      <c r="F25" s="106"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="106"/>
-      <c r="I25" s="106"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="106"/>
-      <c r="L25" s="106"/>
-      <c r="M25" s="106"/>
-      <c r="N25" s="106"/>
-      <c r="O25" s="106"/>
-      <c r="P25" s="106"/>
-      <c r="Q25" s="106"/>
-      <c r="R25" s="106"/>
-      <c r="S25" s="106"/>
-      <c r="T25" s="106"/>
-      <c r="U25" s="106"/>
-      <c r="V25" s="106"/>
-      <c r="W25" s="106"/>
-      <c r="X25" s="106"/>
-      <c r="Y25" s="107"/>
+      <c r="D25" s="99"/>
+      <c r="E25" s="99"/>
+      <c r="F25" s="99"/>
+      <c r="G25" s="99"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="99"/>
+      <c r="N25" s="99"/>
+      <c r="O25" s="99"/>
+      <c r="P25" s="99"/>
+      <c r="Q25" s="99"/>
+      <c r="R25" s="99"/>
+      <c r="S25" s="99"/>
+      <c r="T25" s="99"/>
+      <c r="U25" s="99"/>
+      <c r="V25" s="99"/>
+      <c r="W25" s="99"/>
+      <c r="X25" s="99"/>
+      <c r="Y25" s="100"/>
     </row>
     <row r="26" spans="1:25" ht="16.5" customHeight="1">
-      <c r="B26" s="100"/>
+      <c r="B26" s="93"/>
       <c r="C26" s="15"/>
-      <c r="D26" s="104" t="s">
+      <c r="D26" s="97" t="s">
         <v>668</v>
       </c>
       <c r="E26" s="15"/>
@@ -15067,12 +15078,12 @@
       <c r="V26" s="15"/>
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
-      <c r="Y26" s="103"/>
+      <c r="Y26" s="96"/>
     </row>
     <row r="27" spans="1:25" ht="16.5" customHeight="1">
-      <c r="B27" s="100"/>
+      <c r="B27" s="93"/>
       <c r="C27" s="15"/>
-      <c r="D27" s="104" t="s">
+      <c r="D27" s="97" t="s">
         <v>669</v>
       </c>
       <c r="E27" s="15"/>
@@ -15095,39 +15106,39 @@
       <c r="V27" s="15"/>
       <c r="W27" s="15"/>
       <c r="X27" s="15"/>
-      <c r="Y27" s="103"/>
+      <c r="Y27" s="96"/>
     </row>
     <row r="28" spans="1:25" ht="16.5" customHeight="1" thickBot="1">
-      <c r="B28" s="108"/>
-      <c r="C28" s="109"/>
-      <c r="D28" s="110" t="s">
+      <c r="B28" s="101"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="103" t="s">
         <v>670</v>
       </c>
-      <c r="E28" s="109"/>
-      <c r="F28" s="109"/>
-      <c r="G28" s="109"/>
-      <c r="H28" s="109"/>
-      <c r="I28" s="109"/>
-      <c r="J28" s="109"/>
-      <c r="K28" s="109"/>
-      <c r="L28" s="109"/>
-      <c r="M28" s="109"/>
-      <c r="N28" s="109"/>
-      <c r="O28" s="109"/>
-      <c r="P28" s="109"/>
-      <c r="Q28" s="109"/>
-      <c r="R28" s="109"/>
-      <c r="S28" s="109"/>
-      <c r="T28" s="109"/>
-      <c r="U28" s="109"/>
-      <c r="V28" s="109"/>
-      <c r="W28" s="109"/>
-      <c r="X28" s="109"/>
-      <c r="Y28" s="111"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="102"/>
+      <c r="G28" s="102"/>
+      <c r="H28" s="102"/>
+      <c r="I28" s="102"/>
+      <c r="J28" s="102"/>
+      <c r="K28" s="102"/>
+      <c r="L28" s="102"/>
+      <c r="M28" s="102"/>
+      <c r="N28" s="102"/>
+      <c r="O28" s="102"/>
+      <c r="P28" s="102"/>
+      <c r="Q28" s="102"/>
+      <c r="R28" s="102"/>
+      <c r="S28" s="102"/>
+      <c r="T28" s="102"/>
+      <c r="U28" s="102"/>
+      <c r="V28" s="102"/>
+      <c r="W28" s="102"/>
+      <c r="X28" s="102"/>
+      <c r="Y28" s="104"/>
     </row>
     <row r="29" spans="1:25" ht="16.5" customHeight="1" thickBot="1"/>
-    <row r="30" spans="1:25" s="113" customFormat="1" ht="15" thickBot="1">
-      <c r="A30" s="112"/>
+    <row r="30" spans="1:25" s="106" customFormat="1" ht="15" thickBot="1">
+      <c r="A30" s="105"/>
     </row>
     <row r="31" spans="1:25" ht="23.25">
       <c r="B31" s="64" t="s">
@@ -15158,451 +15169,451 @@
       <c r="C36" s="81" t="s">
         <v>674</v>
       </c>
-      <c r="AJ36" s="114" t="s">
+      <c r="AJ36" s="107" t="s">
         <v>675</v>
       </c>
-      <c r="AK36" s="115"/>
-      <c r="AL36" s="115"/>
-      <c r="AM36" s="115"/>
-      <c r="AN36" s="115"/>
-      <c r="AO36" s="115"/>
-      <c r="AP36" s="115"/>
-      <c r="AQ36" s="115"/>
-      <c r="AR36" s="115"/>
-      <c r="AS36" s="115"/>
-      <c r="AT36" s="115"/>
-      <c r="AU36" s="115"/>
-      <c r="AV36" s="115"/>
-      <c r="AW36" s="115"/>
-      <c r="AX36" s="115"/>
-      <c r="AY36" s="115"/>
-      <c r="AZ36" s="115"/>
-      <c r="BA36" s="115"/>
-      <c r="BB36" s="116"/>
+      <c r="AK36" s="108"/>
+      <c r="AL36" s="108"/>
+      <c r="AM36" s="108"/>
+      <c r="AN36" s="108"/>
+      <c r="AO36" s="108"/>
+      <c r="AP36" s="108"/>
+      <c r="AQ36" s="108"/>
+      <c r="AR36" s="108"/>
+      <c r="AS36" s="108"/>
+      <c r="AT36" s="108"/>
+      <c r="AU36" s="108"/>
+      <c r="AV36" s="108"/>
+      <c r="AW36" s="108"/>
+      <c r="AX36" s="108"/>
+      <c r="AY36" s="108"/>
+      <c r="AZ36" s="108"/>
+      <c r="BA36" s="108"/>
+      <c r="BB36" s="109"/>
     </row>
     <row r="37" spans="3:74">
       <c r="C37" s="67" t="s">
         <v>676</v>
       </c>
-      <c r="AJ37" s="117" t="s">
+      <c r="AJ37" s="110" t="s">
         <v>677</v>
       </c>
-      <c r="BB37" s="118"/>
+      <c r="BB37" s="111"/>
     </row>
     <row r="38" spans="3:74">
       <c r="C38" s="67" t="s">
         <v>678</v>
       </c>
-      <c r="AJ38" s="119" t="s">
+      <c r="AJ38" s="112" t="s">
         <v>679</v>
       </c>
-      <c r="BB38" s="118"/>
+      <c r="BB38" s="111"/>
     </row>
     <row r="39" spans="3:74">
       <c r="C39" s="81" t="s">
         <v>680</v>
       </c>
-      <c r="AJ39" s="119" t="s">
+      <c r="AJ39" s="112" t="s">
         <v>681</v>
       </c>
-      <c r="BB39" s="118"/>
+      <c r="BB39" s="111"/>
     </row>
     <row r="40" spans="3:74">
       <c r="C40" s="67" t="s">
         <v>682</v>
       </c>
-      <c r="AJ40" s="119" t="s">
+      <c r="AJ40" s="112" t="s">
         <v>683</v>
       </c>
-      <c r="BB40" s="118"/>
+      <c r="BB40" s="111"/>
     </row>
     <row r="41" spans="3:74">
       <c r="C41" s="67" t="s">
         <v>684</v>
       </c>
-      <c r="AJ41" s="119" t="s">
+      <c r="AJ41" s="112" t="s">
         <v>685</v>
       </c>
-      <c r="BB41" s="118"/>
+      <c r="BB41" s="111"/>
     </row>
     <row r="42" spans="3:74" ht="15" thickBot="1">
       <c r="C42" s="67" t="s">
         <v>686</v>
       </c>
-      <c r="AJ42" s="119" t="s">
+      <c r="AJ42" s="112" t="s">
         <v>687</v>
       </c>
-      <c r="BB42" s="118"/>
+      <c r="BB42" s="111"/>
     </row>
     <row r="43" spans="3:74">
       <c r="C43" s="63"/>
-      <c r="AJ43" s="119" t="s">
+      <c r="AJ43" s="112" t="s">
         <v>688</v>
       </c>
-      <c r="BB43" s="118"/>
-      <c r="BE43" s="120" t="s">
+      <c r="BB43" s="111"/>
+      <c r="BE43" s="113" t="s">
         <v>689</v>
       </c>
-      <c r="BF43" s="115"/>
-      <c r="BG43" s="115"/>
-      <c r="BH43" s="115"/>
-      <c r="BI43" s="115"/>
-      <c r="BJ43" s="115"/>
-      <c r="BK43" s="115"/>
-      <c r="BL43" s="115"/>
-      <c r="BM43" s="115"/>
-      <c r="BN43" s="115"/>
-      <c r="BO43" s="115"/>
-      <c r="BP43" s="115"/>
-      <c r="BQ43" s="115"/>
-      <c r="BR43" s="115"/>
-      <c r="BS43" s="115"/>
-      <c r="BT43" s="115"/>
-      <c r="BU43" s="115"/>
-      <c r="BV43" s="116"/>
+      <c r="BF43" s="108"/>
+      <c r="BG43" s="108"/>
+      <c r="BH43" s="108"/>
+      <c r="BI43" s="108"/>
+      <c r="BJ43" s="108"/>
+      <c r="BK43" s="108"/>
+      <c r="BL43" s="108"/>
+      <c r="BM43" s="108"/>
+      <c r="BN43" s="108"/>
+      <c r="BO43" s="108"/>
+      <c r="BP43" s="108"/>
+      <c r="BQ43" s="108"/>
+      <c r="BR43" s="108"/>
+      <c r="BS43" s="108"/>
+      <c r="BT43" s="108"/>
+      <c r="BU43" s="108"/>
+      <c r="BV43" s="109"/>
     </row>
     <row r="44" spans="3:74">
-      <c r="C44" s="121" t="s">
+      <c r="C44" s="114" t="s">
         <v>690</v>
       </c>
-      <c r="AJ44" s="119" t="s">
+      <c r="AJ44" s="112" t="s">
         <v>691</v>
       </c>
-      <c r="BB44" s="118"/>
-      <c r="BE44" s="122" t="s">
+      <c r="BB44" s="111"/>
+      <c r="BE44" s="115" t="s">
         <v>692</v>
       </c>
-      <c r="BV44" s="118"/>
+      <c r="BV44" s="111"/>
     </row>
     <row r="45" spans="3:74" ht="17.25">
       <c r="C45" s="67" t="s">
         <v>693</v>
       </c>
-      <c r="AJ45" s="123" t="s">
+      <c r="AJ45" s="116" t="s">
         <v>694</v>
       </c>
-      <c r="BB45" s="118"/>
-      <c r="BE45" s="124" t="s">
+      <c r="BB45" s="111"/>
+      <c r="BE45" s="117" t="s">
         <v>695</v>
       </c>
-      <c r="BV45" s="118"/>
+      <c r="BV45" s="111"/>
     </row>
     <row r="46" spans="3:74">
       <c r="C46" s="67" t="s">
         <v>696</v>
       </c>
-      <c r="AJ46" s="117" t="s">
+      <c r="AJ46" s="110" t="s">
         <v>697</v>
       </c>
-      <c r="BB46" s="118"/>
-      <c r="BE46" s="125" t="s">
+      <c r="BB46" s="111"/>
+      <c r="BE46" s="118" t="s">
         <v>698</v>
       </c>
-      <c r="BV46" s="118"/>
+      <c r="BV46" s="111"/>
     </row>
     <row r="47" spans="3:74">
       <c r="C47" s="67" t="s">
         <v>699</v>
       </c>
-      <c r="AJ47" s="126" t="s">
+      <c r="AJ47" s="119" t="s">
         <v>700</v>
       </c>
-      <c r="BB47" s="118"/>
-      <c r="BE47" s="125" t="s">
+      <c r="BB47" s="111"/>
+      <c r="BE47" s="118" t="s">
         <v>701</v>
       </c>
-      <c r="BV47" s="118"/>
+      <c r="BV47" s="111"/>
     </row>
     <row r="48" spans="3:74" ht="15.75" thickBot="1">
-      <c r="C48" s="127" t="s">
+      <c r="C48" s="120" t="s">
         <v>702</v>
       </c>
-      <c r="AJ48" s="128" t="s">
+      <c r="AJ48" s="121" t="s">
         <v>703</v>
       </c>
-      <c r="AK48" s="129"/>
-      <c r="AL48" s="129"/>
-      <c r="AM48" s="129"/>
-      <c r="AN48" s="129"/>
-      <c r="AO48" s="129"/>
-      <c r="AP48" s="129"/>
-      <c r="AQ48" s="129"/>
-      <c r="AR48" s="129"/>
-      <c r="AS48" s="129"/>
-      <c r="AT48" s="129"/>
-      <c r="AU48" s="129"/>
-      <c r="AV48" s="129"/>
-      <c r="AW48" s="129"/>
-      <c r="AX48" s="129"/>
-      <c r="AY48" s="129"/>
-      <c r="AZ48" s="129"/>
-      <c r="BA48" s="129"/>
-      <c r="BB48" s="130"/>
-      <c r="BE48" s="125" t="s">
+      <c r="AK48" s="122"/>
+      <c r="AL48" s="122"/>
+      <c r="AM48" s="122"/>
+      <c r="AN48" s="122"/>
+      <c r="AO48" s="122"/>
+      <c r="AP48" s="122"/>
+      <c r="AQ48" s="122"/>
+      <c r="AR48" s="122"/>
+      <c r="AS48" s="122"/>
+      <c r="AT48" s="122"/>
+      <c r="AU48" s="122"/>
+      <c r="AV48" s="122"/>
+      <c r="AW48" s="122"/>
+      <c r="AX48" s="122"/>
+      <c r="AY48" s="122"/>
+      <c r="AZ48" s="122"/>
+      <c r="BA48" s="122"/>
+      <c r="BB48" s="123"/>
+      <c r="BE48" s="118" t="s">
         <v>704</v>
       </c>
-      <c r="BV48" s="118"/>
+      <c r="BV48" s="111"/>
     </row>
     <row r="49" spans="2:74" ht="15">
       <c r="C49" s="67" t="s">
         <v>705</v>
       </c>
-      <c r="BE49" s="124" t="s">
+      <c r="BE49" s="117" t="s">
         <v>706</v>
       </c>
-      <c r="BV49" s="118"/>
+      <c r="BV49" s="111"/>
     </row>
     <row r="50" spans="2:74" ht="15" thickBot="1">
       <c r="C50" s="67" t="s">
         <v>707</v>
       </c>
-      <c r="BE50" s="125" t="s">
+      <c r="BE50" s="118" t="s">
         <v>708</v>
       </c>
-      <c r="BV50" s="118"/>
+      <c r="BV50" s="111"/>
     </row>
     <row r="51" spans="2:74" ht="17.25">
       <c r="C51" s="67" t="s">
         <v>709</v>
       </c>
-      <c r="AA51" s="114" t="s">
+      <c r="AA51" s="107" t="s">
         <v>710</v>
       </c>
-      <c r="AB51" s="115"/>
-      <c r="AC51" s="115"/>
-      <c r="AD51" s="115"/>
-      <c r="AE51" s="115"/>
-      <c r="AF51" s="115"/>
-      <c r="AG51" s="115"/>
-      <c r="AH51" s="115"/>
-      <c r="AI51" s="115"/>
-      <c r="AJ51" s="115"/>
-      <c r="AK51" s="115"/>
-      <c r="AL51" s="115"/>
-      <c r="AM51" s="115"/>
-      <c r="AN51" s="115"/>
-      <c r="AO51" s="115"/>
-      <c r="AP51" s="115"/>
-      <c r="AQ51" s="115"/>
-      <c r="AR51" s="115"/>
-      <c r="AS51" s="115"/>
-      <c r="AT51" s="115"/>
-      <c r="AU51" s="115"/>
-      <c r="AV51" s="115"/>
-      <c r="AW51" s="115"/>
-      <c r="AX51" s="115"/>
-      <c r="AY51" s="115"/>
-      <c r="AZ51" s="115"/>
-      <c r="BA51" s="115"/>
-      <c r="BB51" s="115"/>
-      <c r="BC51" s="116"/>
-      <c r="BE51" s="125" t="s">
+      <c r="AB51" s="108"/>
+      <c r="AC51" s="108"/>
+      <c r="AD51" s="108"/>
+      <c r="AE51" s="108"/>
+      <c r="AF51" s="108"/>
+      <c r="AG51" s="108"/>
+      <c r="AH51" s="108"/>
+      <c r="AI51" s="108"/>
+      <c r="AJ51" s="108"/>
+      <c r="AK51" s="108"/>
+      <c r="AL51" s="108"/>
+      <c r="AM51" s="108"/>
+      <c r="AN51" s="108"/>
+      <c r="AO51" s="108"/>
+      <c r="AP51" s="108"/>
+      <c r="AQ51" s="108"/>
+      <c r="AR51" s="108"/>
+      <c r="AS51" s="108"/>
+      <c r="AT51" s="108"/>
+      <c r="AU51" s="108"/>
+      <c r="AV51" s="108"/>
+      <c r="AW51" s="108"/>
+      <c r="AX51" s="108"/>
+      <c r="AY51" s="108"/>
+      <c r="AZ51" s="108"/>
+      <c r="BA51" s="108"/>
+      <c r="BB51" s="108"/>
+      <c r="BC51" s="109"/>
+      <c r="BE51" s="118" t="s">
         <v>711</v>
       </c>
-      <c r="BV51" s="118"/>
+      <c r="BV51" s="111"/>
     </row>
     <row r="52" spans="2:74">
       <c r="C52" s="67" t="s">
         <v>712</v>
       </c>
-      <c r="AA52" s="131" t="s">
+      <c r="AA52" s="124" t="s">
         <v>713</v>
       </c>
-      <c r="BC52" s="118"/>
-      <c r="BE52" s="125" t="s">
+      <c r="BC52" s="111"/>
+      <c r="BE52" s="118" t="s">
         <v>714</v>
       </c>
-      <c r="BV52" s="118"/>
+      <c r="BV52" s="111"/>
     </row>
     <row r="53" spans="2:74">
       <c r="C53" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="AA53" s="131"/>
+      <c r="AA53" s="124"/>
       <c r="AB53" s="20" t="s">
         <v>715</v>
       </c>
-      <c r="BC53" s="118"/>
-      <c r="BE53" s="125"/>
-      <c r="BV53" s="118"/>
+      <c r="BC53" s="111"/>
+      <c r="BE53" s="118"/>
+      <c r="BV53" s="111"/>
     </row>
     <row r="54" spans="2:74">
       <c r="C54" s="67" t="s">
         <v>716</v>
       </c>
-      <c r="AA54" s="125"/>
+      <c r="AA54" s="118"/>
       <c r="AB54" s="20" t="s">
         <v>717</v>
       </c>
-      <c r="BC54" s="118"/>
-      <c r="BE54" s="132" t="s">
+      <c r="BC54" s="111"/>
+      <c r="BE54" s="125" t="s">
         <v>718</v>
       </c>
-      <c r="BV54" s="118"/>
+      <c r="BV54" s="111"/>
     </row>
     <row r="55" spans="2:74">
       <c r="C55" s="67" t="s">
         <v>719</v>
       </c>
-      <c r="AA55" s="131"/>
+      <c r="AA55" s="124"/>
       <c r="AB55" s="20" t="s">
         <v>720</v>
       </c>
-      <c r="BC55" s="118"/>
-      <c r="BE55" s="122" t="s">
+      <c r="BC55" s="111"/>
+      <c r="BE55" s="115" t="s">
         <v>721</v>
       </c>
-      <c r="BV55" s="118"/>
+      <c r="BV55" s="111"/>
     </row>
     <row r="56" spans="2:74" ht="17.25">
       <c r="C56" s="67" t="s">
         <v>722</v>
       </c>
-      <c r="AA56" s="123" t="s">
+      <c r="AA56" s="116" t="s">
         <v>723</v>
       </c>
-      <c r="BC56" s="118"/>
-      <c r="BE56" s="124" t="s">
+      <c r="BC56" s="111"/>
+      <c r="BE56" s="117" t="s">
         <v>695</v>
       </c>
-      <c r="BV56" s="118"/>
+      <c r="BV56" s="111"/>
     </row>
     <row r="57" spans="2:74">
       <c r="C57" s="67" t="s">
         <v>724</v>
       </c>
-      <c r="AA57" s="133"/>
-      <c r="AB57" s="134" t="s">
+      <c r="AA57" s="126"/>
+      <c r="AB57" s="127" t="s">
         <v>725</v>
       </c>
-      <c r="BC57" s="118"/>
-      <c r="BE57" s="125" t="s">
+      <c r="BC57" s="111"/>
+      <c r="BE57" s="118" t="s">
         <v>726</v>
       </c>
-      <c r="BV57" s="118"/>
+      <c r="BV57" s="111"/>
     </row>
     <row r="58" spans="2:74">
       <c r="C58" s="67" t="s">
         <v>727</v>
       </c>
-      <c r="AA58" s="135"/>
-      <c r="AB58" s="136" t="s">
+      <c r="AA58" s="128"/>
+      <c r="AB58" s="129" t="s">
         <v>728</v>
       </c>
-      <c r="BC58" s="118"/>
-      <c r="BE58" s="125" t="s">
+      <c r="BC58" s="111"/>
+      <c r="BE58" s="118" t="s">
         <v>729</v>
       </c>
-      <c r="BV58" s="118"/>
+      <c r="BV58" s="111"/>
     </row>
     <row r="59" spans="2:74">
       <c r="C59" s="67" t="s">
         <v>730</v>
       </c>
-      <c r="AA59" s="131"/>
-      <c r="AB59" s="136" t="s">
+      <c r="AA59" s="124"/>
+      <c r="AB59" s="129" t="s">
         <v>731</v>
       </c>
-      <c r="BC59" s="118"/>
-      <c r="BE59" s="125" t="s">
+      <c r="BC59" s="111"/>
+      <c r="BE59" s="118" t="s">
         <v>732</v>
       </c>
-      <c r="BV59" s="118"/>
+      <c r="BV59" s="111"/>
     </row>
     <row r="60" spans="2:74" ht="15">
       <c r="C60" s="67" t="s">
         <v>156</v>
       </c>
-      <c r="AA60" s="131"/>
-      <c r="AB60" s="134" t="s">
+      <c r="AA60" s="124"/>
+      <c r="AB60" s="127" t="s">
         <v>733</v>
       </c>
-      <c r="BC60" s="118"/>
-      <c r="BE60" s="124" t="s">
+      <c r="BC60" s="111"/>
+      <c r="BE60" s="117" t="s">
         <v>706</v>
       </c>
-      <c r="BV60" s="118"/>
+      <c r="BV60" s="111"/>
     </row>
     <row r="61" spans="2:74">
-      <c r="AA61" s="131"/>
-      <c r="AB61" s="137" t="s">
+      <c r="AA61" s="124"/>
+      <c r="AB61" s="130" t="s">
         <v>734</v>
       </c>
-      <c r="BC61" s="118"/>
-      <c r="BE61" s="125" t="s">
+      <c r="BC61" s="111"/>
+      <c r="BE61" s="118" t="s">
         <v>735</v>
       </c>
-      <c r="BV61" s="118"/>
+      <c r="BV61" s="111"/>
     </row>
     <row r="62" spans="2:74" ht="17.25">
       <c r="B62" s="78" t="s">
         <v>645</v>
       </c>
-      <c r="AA62" s="131"/>
-      <c r="AB62" s="134" t="s">
+      <c r="AA62" s="124"/>
+      <c r="AB62" s="127" t="s">
         <v>736</v>
       </c>
-      <c r="BC62" s="118"/>
-      <c r="BE62" s="125" t="s">
+      <c r="BC62" s="111"/>
+      <c r="BE62" s="118" t="s">
         <v>737</v>
       </c>
-      <c r="BV62" s="118"/>
+      <c r="BV62" s="111"/>
     </row>
     <row r="63" spans="2:74" ht="15" thickBot="1">
       <c r="C63" s="81" t="s">
         <v>738</v>
       </c>
-      <c r="AA63" s="138"/>
-      <c r="AB63" s="139" t="s">
+      <c r="AA63" s="131"/>
+      <c r="AB63" s="132" t="s">
         <v>739</v>
       </c>
-      <c r="AC63" s="129"/>
-      <c r="AD63" s="129"/>
-      <c r="AE63" s="129"/>
-      <c r="AF63" s="129"/>
-      <c r="AG63" s="129"/>
-      <c r="AH63" s="129"/>
-      <c r="AI63" s="129"/>
-      <c r="AJ63" s="129"/>
-      <c r="AK63" s="129"/>
-      <c r="AL63" s="129"/>
-      <c r="AM63" s="129"/>
-      <c r="AN63" s="129"/>
-      <c r="AO63" s="129"/>
-      <c r="AP63" s="129"/>
-      <c r="AQ63" s="129"/>
-      <c r="AR63" s="129"/>
-      <c r="AS63" s="129"/>
-      <c r="AT63" s="129"/>
-      <c r="AU63" s="129"/>
-      <c r="AV63" s="129"/>
-      <c r="AW63" s="129"/>
-      <c r="AX63" s="129"/>
-      <c r="AY63" s="129"/>
-      <c r="AZ63" s="129"/>
-      <c r="BA63" s="129"/>
-      <c r="BB63" s="129"/>
-      <c r="BC63" s="130"/>
-      <c r="BE63" s="140" t="s">
+      <c r="AC63" s="122"/>
+      <c r="AD63" s="122"/>
+      <c r="AE63" s="122"/>
+      <c r="AF63" s="122"/>
+      <c r="AG63" s="122"/>
+      <c r="AH63" s="122"/>
+      <c r="AI63" s="122"/>
+      <c r="AJ63" s="122"/>
+      <c r="AK63" s="122"/>
+      <c r="AL63" s="122"/>
+      <c r="AM63" s="122"/>
+      <c r="AN63" s="122"/>
+      <c r="AO63" s="122"/>
+      <c r="AP63" s="122"/>
+      <c r="AQ63" s="122"/>
+      <c r="AR63" s="122"/>
+      <c r="AS63" s="122"/>
+      <c r="AT63" s="122"/>
+      <c r="AU63" s="122"/>
+      <c r="AV63" s="122"/>
+      <c r="AW63" s="122"/>
+      <c r="AX63" s="122"/>
+      <c r="AY63" s="122"/>
+      <c r="AZ63" s="122"/>
+      <c r="BA63" s="122"/>
+      <c r="BB63" s="122"/>
+      <c r="BC63" s="123"/>
+      <c r="BE63" s="133" t="s">
         <v>740</v>
       </c>
-      <c r="BF63" s="129"/>
-      <c r="BG63" s="129"/>
-      <c r="BH63" s="129"/>
-      <c r="BI63" s="129"/>
-      <c r="BJ63" s="129"/>
-      <c r="BK63" s="129"/>
-      <c r="BL63" s="129"/>
-      <c r="BM63" s="129"/>
-      <c r="BN63" s="129"/>
-      <c r="BO63" s="129"/>
-      <c r="BP63" s="129"/>
-      <c r="BQ63" s="129"/>
-      <c r="BR63" s="129"/>
-      <c r="BS63" s="129"/>
-      <c r="BT63" s="129"/>
-      <c r="BU63" s="129"/>
-      <c r="BV63" s="130"/>
+      <c r="BF63" s="122"/>
+      <c r="BG63" s="122"/>
+      <c r="BH63" s="122"/>
+      <c r="BI63" s="122"/>
+      <c r="BJ63" s="122"/>
+      <c r="BK63" s="122"/>
+      <c r="BL63" s="122"/>
+      <c r="BM63" s="122"/>
+      <c r="BN63" s="122"/>
+      <c r="BO63" s="122"/>
+      <c r="BP63" s="122"/>
+      <c r="BQ63" s="122"/>
+      <c r="BR63" s="122"/>
+      <c r="BS63" s="122"/>
+      <c r="BT63" s="122"/>
+      <c r="BU63" s="122"/>
+      <c r="BV63" s="123"/>
     </row>
     <row r="64" spans="2:74">
       <c r="C64" s="67" t="s">
@@ -15623,7 +15634,7 @@
       <c r="C67" s="63"/>
     </row>
     <row r="68" spans="2:47">
-      <c r="C68" s="121" t="s">
+      <c r="C68" s="114" t="s">
         <v>744</v>
       </c>
     </row>
@@ -15644,7 +15655,7 @@
       </c>
     </row>
     <row r="73" spans="2:47">
-      <c r="C73" s="121" t="s">
+      <c r="C73" s="114" t="s">
         <v>745</v>
       </c>
       <c r="V73" s="81" t="s">
@@ -15716,7 +15727,7 @@
       <c r="V79" s="67" t="s">
         <v>764</v>
       </c>
-      <c r="AU79" s="127" t="s">
+      <c r="AU79" s="120" t="s">
         <v>765</v>
       </c>
     </row>
@@ -15801,7 +15812,7 @@
       <c r="C87" s="67" t="s">
         <v>784</v>
       </c>
-      <c r="V87" s="127" t="s">
+      <c r="V87" s="120" t="s">
         <v>702</v>
       </c>
       <c r="AU87" s="67" t="s">
@@ -15839,7 +15850,7 @@
       </c>
     </row>
     <row r="91" spans="3:47" ht="15">
-      <c r="C91" s="127" t="s">
+      <c r="C91" s="120" t="s">
         <v>702</v>
       </c>
       <c r="V91" s="67" t="s">
@@ -16047,10 +16058,10 @@
       </c>
     </row>
     <row r="126" spans="2:31">
-      <c r="C126" s="121" t="s">
+      <c r="C126" s="114" t="s">
         <v>821</v>
       </c>
-      <c r="AE126" s="121" t="s">
+      <c r="AE126" s="114" t="s">
         <v>822</v>
       </c>
     </row>
@@ -16104,7 +16115,7 @@
     </row>
     <row r="133" spans="3:31" ht="15">
       <c r="C133" s="63"/>
-      <c r="AE133" s="127" t="s">
+      <c r="AE133" s="120" t="s">
         <v>765</v>
       </c>
     </row>
@@ -16141,17 +16152,17 @@
       </c>
     </row>
     <row r="138" spans="3:31" ht="15">
-      <c r="C138" s="127" t="s">
+      <c r="C138" s="120" t="s">
         <v>702</v>
       </c>
-      <c r="U138" s="141"/>
+      <c r="U138" s="134"/>
       <c r="AE138" s="67" t="s">
         <v>840</v>
       </c>
     </row>
     <row r="139" spans="3:31">
       <c r="C139" s="67"/>
-      <c r="D139" s="142" t="s">
+      <c r="D139" s="135" t="s">
         <v>841</v>
       </c>
       <c r="AE139" s="67" t="s">
@@ -16211,7 +16222,7 @@
     </row>
     <row r="146" spans="3:31">
       <c r="C146" s="67"/>
-      <c r="D146" s="142" t="s">
+      <c r="D146" s="135" t="s">
         <v>848</v>
       </c>
       <c r="AE146" s="67" t="s">
@@ -16310,7 +16321,7 @@
       <c r="D157" t="s">
         <v>484</v>
       </c>
-      <c r="AE157" s="143" t="s">
+      <c r="AE157" s="136" t="s">
         <v>865</v>
       </c>
     </row>
@@ -16319,7 +16330,7 @@
       <c r="D158" t="s">
         <v>866</v>
       </c>
-      <c r="AE158" s="143" t="s">
+      <c r="AE158" s="136" t="s">
         <v>867</v>
       </c>
     </row>
@@ -16349,7 +16360,7 @@
     </row>
     <row r="162" spans="2:31">
       <c r="C162" s="67"/>
-      <c r="D162" s="142" t="s">
+      <c r="D162" s="135" t="s">
         <v>870</v>
       </c>
     </row>
@@ -16389,7 +16400,7 @@
       </c>
     </row>
     <row r="169" spans="2:31" ht="15">
-      <c r="AE169" s="127" t="s">
+      <c r="AE169" s="120" t="s">
         <v>702</v>
       </c>
     </row>
@@ -16668,12 +16679,12 @@
       <c r="B217" s="78" t="s">
         <v>658</v>
       </c>
-      <c r="AE217" s="127" t="s">
+      <c r="AE217" s="120" t="s">
         <v>765</v>
       </c>
     </row>
     <row r="218" spans="2:32">
-      <c r="C218" s="121" t="s">
+      <c r="C218" s="114" t="s">
         <v>909</v>
       </c>
       <c r="AF218" s="67" t="s">
@@ -16936,7 +16947,7 @@
       <c r="B263" s="78" t="s">
         <v>660</v>
       </c>
-      <c r="AD263" s="127" t="s">
+      <c r="AD263" s="120" t="s">
         <v>765</v>
       </c>
     </row>
@@ -17067,27 +17078,27 @@
       </c>
     </row>
     <row r="285" spans="31:31">
-      <c r="AE285" s="143" t="s">
+      <c r="AE285" s="136" t="s">
         <v>883</v>
       </c>
     </row>
     <row r="286" spans="31:31">
-      <c r="AE286" s="143" t="s">
+      <c r="AE286" s="136" t="s">
         <v>963</v>
       </c>
     </row>
     <row r="287" spans="31:31">
-      <c r="AE287" s="143" t="s">
+      <c r="AE287" s="136" t="s">
         <v>964</v>
       </c>
     </row>
     <row r="288" spans="31:31">
-      <c r="AE288" s="143" t="s">
+      <c r="AE288" s="136" t="s">
         <v>965</v>
       </c>
     </row>
     <row r="289" spans="31:31">
-      <c r="AE289" s="143" t="s">
+      <c r="AE289" s="136" t="s">
         <v>4</v>
       </c>
     </row>
@@ -17217,7 +17228,7 @@
       </c>
     </row>
     <row r="316" spans="2:31" ht="15">
-      <c r="C316" s="144" t="s">
+      <c r="C316" s="137" t="s">
         <v>979</v>
       </c>
     </row>
@@ -17280,13 +17291,13 @@
       <c r="D328" s="67"/>
     </row>
     <row r="329" spans="2:6" ht="18">
-      <c r="B329" s="145" t="s">
+      <c r="B329" s="138" t="s">
         <v>990</v>
       </c>
       <c r="D329" s="67"/>
     </row>
     <row r="330" spans="2:6" ht="15">
-      <c r="C330" s="144" t="s">
+      <c r="C330" s="137" t="s">
         <v>991</v>
       </c>
     </row>
@@ -17387,7 +17398,7 @@
       <c r="B350" s="64" t="s">
         <v>663</v>
       </c>
-      <c r="AE350" s="127" t="s">
+      <c r="AE350" s="120" t="s">
         <v>765</v>
       </c>
     </row>
@@ -17555,7 +17566,7 @@
       <c r="B379" s="64" t="s">
         <v>665</v>
       </c>
-      <c r="AC379" s="127" t="s">
+      <c r="AC379" s="120" t="s">
         <v>1029</v>
       </c>
     </row>

--- a/unit8_device_tree/unit8_device_tree.xlsx
+++ b/unit8_device_tree/unit8_device_tree.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Game\Linux\unit8_device_tree\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD3B225-04AA-4450-80F1-7AC160AD8C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EA14E1-A5F9-46A6-829C-1F3B6360FCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{4DED5FC3-1A0F-4534-A4A0-3DE5C8B952C4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="1" r:id="rId1"/>
@@ -20,21 +20,10 @@
     <sheet name="DTtoDriverMappingSequence" sheetId="7" r:id="rId5"/>
     <sheet name="deviceTree api" sheetId="8" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -7408,7 +7397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B049B0C-149B-43FC-9295-D712528C5BE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7419,7 +7408,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{860E8409-845C-4194-9F3A-26496BEE109C}"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -7427,7 +7416,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B119285-9151-4AA2-914C-9168F431DB10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:T178"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -9864,7 +9853,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{818AFC5C-713F-4650-8653-9D59B0A25DCF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:M91"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10387,7 +10376,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72766B5E-4D24-43F4-8273-B4BBE31EB2E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:R106"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -11972,7 +11961,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E393CC-C9BE-4713-8317-003849BCB02B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BT494"/>
   <sheetFormatPr defaultColWidth="2.75" defaultRowHeight="14.25"/>
   <cols>
@@ -14352,7 +14341,7 @@
     <mergeCell ref="AA12:AD12"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B5" location="'gpio BBB'!A1" display="1.1 Device Tree Source (.dts)" xr:uid="{AF2CD107-6249-4937-9A23-4E39D12D5B20}"/>
+    <hyperlink ref="B5" location="'gpio BBB'!A1" display="1.1 Device Tree Source (.dts)" xr:uid="{00000000-0004-0000-0400-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -14360,7 +14349,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0E6175E-5182-4994-B3D9-82E30CCF48D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BV471"/>
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="14.25"/>
   <sheetData>
@@ -18151,16 +18140,16 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3:O3" location="'deviceTree api'!B31" display="1. NODE HANDLING APIs" xr:uid="{59EB1723-90C1-46F6-9E62-913F08D69B87}"/>
-    <hyperlink ref="C6:P6" location="'deviceTree api'!B70" display="2. PROPERTY READING APIs" xr:uid="{46F04302-E2AD-447F-9A4B-9104C3010990}"/>
-    <hyperlink ref="C10:S10" location="'deviceTree api'!B124" display="3. RESOURCE MANAGEMENT APIs" xr:uid="{CF7F4E4D-6892-4854-9BC9-1EC6FF33BE57}"/>
-    <hyperlink ref="C13:R13" location="'deviceTree api'!B168" display="4. CLOCK MANAGEMENT APIs" xr:uid="{40108E0E-C728-4F81-B8C5-8CB025210C96}"/>
-    <hyperlink ref="C15:I15" location="'deviceTree api'!B216" display="5. GPIO APIs" xr:uid="{CDC30919-12D8-4ED5-9147-2B10397B8894}"/>
-    <hyperlink ref="C17:M17" location="'deviceTree api'!B262" display="6. PINCONTROL APIs" xr:uid="{AB0C68E2-7242-46B3-96A8-C160040BB60B}"/>
-    <hyperlink ref="C21:P21" location="'deviceTree api'!B350" display="8. DEVICE MATCHING APIs" xr:uid="{90EEC3EC-6F2F-4608-AD75-0EFE69EDFC79}"/>
-    <hyperlink ref="C23:Q23" location="'deviceTree api'!B379" display="9. CHILD NODE ITERATION" xr:uid="{739DD18D-4D7C-4BAF-AC78-AF5707B69BAC}"/>
-    <hyperlink ref="C19:R19" location="'deviceTree api'!B329" display="7. PHANDLE &amp; REFERENCE APIs" xr:uid="{D1A5727A-8D0E-4670-85EA-0B18F5991A9B}"/>
-    <hyperlink ref="C25:Y25" location="'deviceTree api'!B423" display="10. BEST PRACTICES &amp; COMMON PATTERNS" xr:uid="{F5140593-C2E7-4198-B58A-A4DB0CBCAFA8}"/>
+    <hyperlink ref="C3:O3" location="'deviceTree api'!B31" display="1. NODE HANDLING APIs" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="C6:P6" location="'deviceTree api'!B70" display="2. PROPERTY READING APIs" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="C10:S10" location="'deviceTree api'!B124" display="3. RESOURCE MANAGEMENT APIs" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="C13:R13" location="'deviceTree api'!B168" display="4. CLOCK MANAGEMENT APIs" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="C15:I15" location="'deviceTree api'!B216" display="5. GPIO APIs" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="C17:M17" location="'deviceTree api'!B262" display="6. PINCONTROL APIs" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="C21:P21" location="'deviceTree api'!B350" display="8. DEVICE MATCHING APIs" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="C23:Q23" location="'deviceTree api'!B379" display="9. CHILD NODE ITERATION" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C19:R19" location="'deviceTree api'!B329" display="7. PHANDLE &amp; REFERENCE APIs" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
+    <hyperlink ref="C25:Y25" location="'deviceTree api'!B423" display="10. BEST PRACTICES &amp; COMMON PATTERNS" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
